--- a/6_손해배상계산/00_양식/입력서.xlsx
+++ b/6_손해배상계산/00_양식/입력서.xlsx
@@ -96,7 +96,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -107,6 +107,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -472,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G91"/>
+  <dimension ref="B2:G93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="2" max="2"/>
@@ -627,41 +628,41 @@
     <row r="17">
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>변론 종결일</t>
+          <t>가동 종료일</t>
         </is>
       </c>
       <c r="D17" s="5" t="n"/>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>보통 비움. 2월 29일생이고 가동연한이 끝나는 해가 평년이면 필수</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>법정이율(%)</t>
+          <t>변론 종결일</t>
         </is>
       </c>
       <c r="D18" s="5" t="n"/>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>기본 5</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>기대여명(년)</t>
+          <t>법정이율(%)</t>
         </is>
       </c>
       <c r="D19" s="5" t="n"/>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>표시용</t>
+          <t>기본 5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>여명 종료일</t>
+          <t>기대여명(년)</t>
         </is>
       </c>
       <c r="D20" s="5" t="n"/>
@@ -671,58 +672,63 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="3" t="inlineStr">
+    <row r="21">
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>여명 종료일</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="n"/>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>가동종료일보다 앞서면 여명단축으로 계산(프로그램 대조 전)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>[일실수입]</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>직종</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="n"/>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>예: 보통인부</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>농촌노임 사용</t>
+          <t>직종</t>
         </is>
       </c>
       <c r="D24" s="5" t="n"/>
       <c r="F24" s="2" t="inlineStr">
         <is>
+          <t>예: 보통인부</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>농촌노임 사용</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="n"/>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
           <t>예 / 아니오</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" s="3" t="inlineStr">
+    <row r="27">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>[기타손해]</t>
         </is>
       </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>기왕 치료비</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="n"/>
     </row>
     <row r="28">
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>기왕 개호비 총일수</t>
+          <t>기왕 치료비</t>
         </is>
       </c>
       <c r="D28" s="5" t="n"/>
@@ -730,7 +736,7 @@
     <row r="29">
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>기왕 개호비 단가</t>
+          <t>기왕 개호비 총일수</t>
         </is>
       </c>
       <c r="D29" s="5" t="n"/>
@@ -738,28 +744,28 @@
     <row r="30">
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>기왕 개호비 실제지출</t>
+          <t>기왕 개호비 단가</t>
         </is>
       </c>
       <c r="D30" s="5" t="n"/>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>실제 지출이 더 적으면 이 금액 적용</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>향후 개호 시작일</t>
+          <t>기왕 개호비 실제지출</t>
         </is>
       </c>
       <c r="D31" s="5" t="n"/>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>실제 지출이 더 적으면 이 금액 적용</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>향후 개호 종료일</t>
+          <t>향후 개호 시작일</t>
         </is>
       </c>
       <c r="D32" s="5" t="n"/>
@@ -767,87 +773,87 @@
     <row r="33">
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>향후 개호 인원</t>
+          <t>향후 개호 종료일</t>
         </is>
       </c>
       <c r="D33" s="5" t="n"/>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>예: 1 또는 0.5</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>향후 개호 기간분할</t>
+          <t>향후 개호 인원</t>
         </is>
       </c>
       <c r="D34" s="5" t="n"/>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>월 단위 / 분기반기 단위 (기본 월 단위)</t>
+          <t>예: 1 또는 0.5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>일실 퇴직금</t>
+          <t>향후 개호 기간분할</t>
         </is>
       </c>
       <c r="D35" s="5" t="n"/>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>직접 계산한 금액</t>
+          <t>월 단위 / 분기반기 단위 (기본 월 단위)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>장례비</t>
+          <t>향후 개호 노임 직종</t>
         </is>
       </c>
       <c r="D36" s="5" t="n"/>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>사망이면 기본 5,000,000</t>
+          <t>향후 개호가 있으면 필수. 노임표 직종명 그대로(예: 보통인부)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>일실 퇴직금</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="n"/>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>직접 계산한 금액</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>장례비</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="n"/>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>사망만. 계산표에 따로 적고 합계에는 넣지 않음</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>[과실상계 · 공제]</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>원고측 과실비율(%)</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="n"/>
-    </row>
-    <row r="40">
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>과실상계 전 공제액</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="n"/>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>산재 휴업급여·장해급여 등</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>지급 치료비</t>
+          <t>원고측 과실비율(%)</t>
         </is>
       </c>
       <c r="D41" s="5" t="n"/>
@@ -855,15 +861,20 @@
     <row r="42">
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>손해배상 선급금</t>
+          <t>과실상계 전 공제액</t>
         </is>
       </c>
       <c r="D42" s="5" t="n"/>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>산재 휴업급여·장해급여 등</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>기타공제 - 비율공제</t>
+          <t>지급 치료비</t>
         </is>
       </c>
       <c r="D43" s="5" t="n"/>
@@ -871,66 +882,70 @@
     <row r="44">
       <c r="B44" s="4" t="inlineStr">
         <is>
+          <t>손해배상 선급금</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="n"/>
+    </row>
+    <row r="45">
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>기타공제 - 비율공제</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="n"/>
+    </row>
+    <row r="46">
+      <c r="B46" s="4" t="inlineStr">
+        <is>
           <t>기타공제 - 전액공제</t>
         </is>
       </c>
-      <c r="D44" s="5" t="n"/>
-    </row>
-    <row r="46">
-      <c r="B46" s="3" t="inlineStr">
+      <c r="D46" s="5" t="n"/>
+    </row>
+    <row r="48">
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>[위자료]</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="B47" s="4" t="inlineStr">
+    <row r="49">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>적용 위자료</t>
         </is>
       </c>
-      <c r="D47" s="5" t="n"/>
-    </row>
-    <row r="49">
-      <c r="B49" s="3" t="inlineStr">
+      <c r="D49" s="5" t="n"/>
+    </row>
+    <row r="51">
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>[노동능력 상실률]</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="B50" s="6" t="inlineStr">
+    <row r="52">
+      <c r="B52" s="6" t="inlineStr">
         <is>
           <t>진료과</t>
         </is>
       </c>
-      <c r="C50" s="6" t="inlineStr">
+      <c r="C52" s="6" t="inlineStr">
         <is>
           <t>개별수치(%)</t>
         </is>
       </c>
-      <c r="D50" s="6" t="inlineStr">
+      <c r="D52" s="6" t="inlineStr">
         <is>
           <t>기왕증(%)</t>
         </is>
       </c>
-      <c r="E50" s="6" t="inlineStr">
+      <c r="E52" s="6" t="inlineStr">
         <is>
           <t>한시장해 년수</t>
         </is>
       </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="7" t="n"/>
-      <c r="C51" s="7" t="n"/>
-      <c r="D51" s="7" t="n"/>
-      <c r="E51" s="7" t="n"/>
-    </row>
-    <row r="52">
-      <c r="B52" s="7" t="n"/>
-      <c r="C52" s="7" t="n"/>
-      <c r="D52" s="7" t="n"/>
-      <c r="E52" s="7" t="n"/>
     </row>
     <row r="53">
       <c r="B53" s="7" t="n"/>
@@ -968,60 +983,56 @@
       <c r="D58" s="7" t="n"/>
       <c r="E58" s="7" t="n"/>
     </row>
+    <row r="59">
+      <c r="B59" s="7" t="n"/>
+      <c r="C59" s="7" t="n"/>
+      <c r="D59" s="7" t="n"/>
+      <c r="E59" s="7" t="n"/>
+    </row>
     <row r="60">
-      <c r="B60" s="3" t="inlineStr">
+      <c r="B60" s="7" t="n"/>
+      <c r="C60" s="7" t="n"/>
+      <c r="D60" s="7" t="n"/>
+      <c r="E60" s="7" t="n"/>
+    </row>
+    <row r="62">
+      <c r="B62" s="3" t="inlineStr">
         <is>
           <t>[향후 치료비]</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="B61" s="6" t="inlineStr">
+    <row r="63">
+      <c r="B63" s="6" t="inlineStr">
         <is>
           <t>종류</t>
         </is>
       </c>
-      <c r="C61" s="6" t="inlineStr">
+      <c r="C63" s="6" t="inlineStr">
         <is>
           <t>비용</t>
         </is>
       </c>
-      <c r="D61" s="6" t="inlineStr">
+      <c r="D63" s="6" t="inlineStr">
         <is>
           <t>최초 필요일</t>
         </is>
       </c>
-      <c r="E61" s="6" t="inlineStr">
+      <c r="E63" s="6" t="inlineStr">
         <is>
           <t>필요 최종일</t>
         </is>
       </c>
-      <c r="F61" s="6" t="inlineStr">
+      <c r="F63" s="6" t="inlineStr">
         <is>
           <t>수명(월)</t>
         </is>
       </c>
-      <c r="G61" s="6" t="inlineStr">
+      <c r="G63" s="6" t="inlineStr">
         <is>
           <t>기왕증(%)</t>
         </is>
       </c>
-    </row>
-    <row r="62">
-      <c r="B62" s="7" t="n"/>
-      <c r="C62" s="7" t="n"/>
-      <c r="D62" s="7" t="n"/>
-      <c r="E62" s="7" t="n"/>
-      <c r="F62" s="7" t="n"/>
-      <c r="G62" s="7" t="n"/>
-    </row>
-    <row r="63">
-      <c r="B63" s="7" t="n"/>
-      <c r="C63" s="7" t="n"/>
-      <c r="D63" s="7" t="n"/>
-      <c r="E63" s="7" t="n"/>
-      <c r="F63" s="7" t="n"/>
-      <c r="G63" s="7" t="n"/>
     </row>
     <row r="64">
       <c r="B64" s="7" t="n"/>
@@ -1071,60 +1082,60 @@
       <c r="F69" s="7" t="n"/>
       <c r="G69" s="7" t="n"/>
     </row>
+    <row r="70">
+      <c r="B70" s="7" t="n"/>
+      <c r="C70" s="7" t="n"/>
+      <c r="D70" s="7" t="n"/>
+      <c r="E70" s="7" t="n"/>
+      <c r="F70" s="7" t="n"/>
+      <c r="G70" s="7" t="n"/>
+    </row>
     <row r="71">
-      <c r="B71" s="3" t="inlineStr">
+      <c r="B71" s="7" t="n"/>
+      <c r="C71" s="7" t="n"/>
+      <c r="D71" s="7" t="n"/>
+      <c r="E71" s="7" t="n"/>
+      <c r="F71" s="7" t="n"/>
+      <c r="G71" s="7" t="n"/>
+    </row>
+    <row r="73">
+      <c r="B73" s="3" t="inlineStr">
         <is>
           <t>[향후 보조구]</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="B72" s="6" t="inlineStr">
+    <row r="74">
+      <c r="B74" s="6" t="inlineStr">
         <is>
           <t>종류</t>
         </is>
       </c>
-      <c r="C72" s="6" t="inlineStr">
+      <c r="C74" s="6" t="inlineStr">
         <is>
           <t>단가</t>
         </is>
       </c>
-      <c r="D72" s="6" t="inlineStr">
+      <c r="D74" s="6" t="inlineStr">
         <is>
           <t>최초 필요일</t>
         </is>
       </c>
-      <c r="E72" s="6" t="inlineStr">
+      <c r="E74" s="6" t="inlineStr">
         <is>
           <t>필요 최종일</t>
         </is>
       </c>
-      <c r="F72" s="6" t="inlineStr">
+      <c r="F74" s="6" t="inlineStr">
         <is>
           <t>수명(월)</t>
         </is>
       </c>
-      <c r="G72" s="6" t="inlineStr">
+      <c r="G74" s="6" t="inlineStr">
         <is>
           <t>기왕증(%)</t>
         </is>
       </c>
-    </row>
-    <row r="73">
-      <c r="B73" s="7" t="n"/>
-      <c r="C73" s="7" t="n"/>
-      <c r="D73" s="7" t="n"/>
-      <c r="E73" s="7" t="n"/>
-      <c r="F73" s="7" t="n"/>
-      <c r="G73" s="7" t="n"/>
-    </row>
-    <row r="74">
-      <c r="B74" s="7" t="n"/>
-      <c r="C74" s="7" t="n"/>
-      <c r="D74" s="7" t="n"/>
-      <c r="E74" s="7" t="n"/>
-      <c r="F74" s="7" t="n"/>
-      <c r="G74" s="7" t="n"/>
     </row>
     <row r="75">
       <c r="B75" s="7" t="n"/>
@@ -1174,56 +1185,77 @@
       <c r="F80" s="7" t="n"/>
       <c r="G80" s="7" t="n"/>
     </row>
+    <row r="81">
+      <c r="B81" s="7" t="n"/>
+      <c r="C81" s="7" t="n"/>
+      <c r="D81" s="7" t="n"/>
+      <c r="E81" s="7" t="n"/>
+      <c r="F81" s="7" t="n"/>
+      <c r="G81" s="7" t="n"/>
+    </row>
     <row r="82">
-      <c r="B82" s="3" t="inlineStr">
+      <c r="B82" s="7" t="n"/>
+      <c r="C82" s="7" t="n"/>
+      <c r="D82" s="7" t="n"/>
+      <c r="E82" s="7" t="n"/>
+      <c r="F82" s="7" t="n"/>
+      <c r="G82" s="7" t="n"/>
+    </row>
+    <row r="84">
+      <c r="B84" s="3" t="inlineStr">
         <is>
           <t>[노임단가 직접입력]</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="B83" s="6" t="inlineStr">
+    <row r="85">
+      <c r="B85" s="6" t="inlineStr">
         <is>
           <t>연도-반기</t>
         </is>
       </c>
-      <c r="C83" s="6" t="inlineStr">
+      <c r="C85" s="6" t="inlineStr">
         <is>
           <t>단가</t>
         </is>
       </c>
-    </row>
-    <row r="84">
-      <c r="B84" s="7" t="n"/>
-      <c r="C84" s="7" t="n"/>
-    </row>
-    <row r="85">
-      <c r="B85" s="7" t="n"/>
-      <c r="C85" s="7" t="n"/>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>예: 2024-1 (연도-반기. 농촌노임이면 연도-분기 1~4)</t>
+        </is>
+      </c>
     </row>
     <row r="86">
-      <c r="B86" s="7" t="n"/>
+      <c r="B86" s="8" t="n"/>
       <c r="C86" s="7" t="n"/>
     </row>
     <row r="87">
-      <c r="B87" s="7" t="n"/>
+      <c r="B87" s="8" t="n"/>
       <c r="C87" s="7" t="n"/>
     </row>
     <row r="88">
-      <c r="B88" s="7" t="n"/>
+      <c r="B88" s="8" t="n"/>
       <c r="C88" s="7" t="n"/>
     </row>
     <row r="89">
-      <c r="B89" s="7" t="n"/>
+      <c r="B89" s="8" t="n"/>
       <c r="C89" s="7" t="n"/>
     </row>
     <row r="90">
-      <c r="B90" s="7" t="n"/>
+      <c r="B90" s="8" t="n"/>
       <c r="C90" s="7" t="n"/>
     </row>
     <row r="91">
-      <c r="B91" s="7" t="n"/>
+      <c r="B91" s="8" t="n"/>
       <c r="C91" s="7" t="n"/>
+    </row>
+    <row r="92">
+      <c r="B92" s="8" t="n"/>
+      <c r="C92" s="7" t="n"/>
+    </row>
+    <row r="93">
+      <c r="B93" s="8" t="n"/>
+      <c r="C93" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
